--- a/database/strategy/advanced_strategy_plan.xlsx
+++ b/database/strategy/advanced_strategy_plan.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>phase_0_single_priority_override</t>
+          <t>phase_1_raiding_bootstrap</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -105,24 +105,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>palace, residence</t>
+          <t>Cranny</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Generated by launcher single-priority override.</t>
+          <t>Village 1 is a small raiding village. Build just enough eco and barracks power for continuous farm-list pressure.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -132,32 +132,1922 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>phase_0_single_priority_override</t>
+          <t>phase_1_raiding_bootstrap</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>building_name</t>
+          <t>resource_fields</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>palace, residence</t>
+          <t>slots 1-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Village 1 is a small raiding village. Build just enough eco and barracks power for continuous farm-list pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>phase_1_raiding_bootstrap</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>barracks, caserne</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Village 1 is a small raiding village. Build just enough eco and barracks power for continuous farm-list pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>phase_1_raiding_bootstrap</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rally point, point de rassemblement</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Generated by launcher single-priority override.</t>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Village 1 is a small raiding village. Build just enough eco and barracks power for continuous farm-list pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>phase_1_raiding_bootstrap</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>main building, batiment principal, b?timent principal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Village 1 is a small raiding village. Build just enough eco and barracks power for continuous farm-list pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>phase_2_raiding_throughput</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>barracks, caserne</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Increase raiding throughput while keeping village compact. Practical target is about 3000 light raiding troops, not a full army village.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>phase_2_raiding_throughput</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>smithy, forge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Increase raiding throughput while keeping village compact. Practical target is about 3000 light raiding troops, not a full army village.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>phase_2_raiding_throughput</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>marketplace, marche, march?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Increase raiding throughput while keeping village compact. Practical target is about 3000 light raiding troops, not a full army village.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>phase_2_raiding_throughput</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Increase raiding throughput while keeping village compact. Practical target is about 3000 light raiding troops, not a full army village.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>phase_3_export_support</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>marketplace, marche, march?</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Logistics phase: use Village 1 marketplace as exporter. Send wood/clay/iron/crop to Village 2 capital continuously via trade routes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>phase_3_export_support</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>warehouse, entrepot, entrep?t</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Logistics phase: use Village 1 marketplace as exporter. Send wood/clay/iron/crop to Village 2 capital continuously via trade routes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>phase_3_export_support</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Logistics phase: use Village 1 marketplace as exporter. Send wood/clay/iron/crop to Village 2 capital continuously via trade routes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>phase_3_export_support</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Logistics phase: use Village 1 marketplace as exporter. Send wood/clay/iron/crop to Village 2 capital continuously via trade routes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>phase_1_capital_stabilize</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>warehouse, entrepot, entrep?t</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Village 2 becomes the capital defensive hub. Stabilize eco and storage immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>phase_1_capital_stabilize</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Village 2 becomes the capital defensive hub. Stabilize eco and storage immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>phase_1_capital_stabilize</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Village 2 becomes the capital defensive hub. Stabilize eco and storage immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>phase_1_capital_stabilize</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>barracks, silo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Village 2 becomes the capital defensive hub. Stabilize eco and storage immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>phase_3_capital_storage_logistics</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>warehouse, entrepot, entrep?t</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Max storage and logistics so capital can absorb imported resources from Village 1 and keep defense queues running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>phase_3_capital_storage_logistics</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Max storage and logistics so capital can absorb imported resources from Village 1 and keep defense queues running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>phase_3_capital_storage_logistics</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>marketplace, marche, march?</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Max storage and logistics so capital can absorb imported resources from Village 1 and keep defense queues running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>phase_3_capital_storage_logistics</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Max storage and logistics so capital can absorb imported resources from Village 1 and keep defense queues running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>phase_1_15c_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Egyptian 15c support village. Build autonomy and storage first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>phase_1_15c_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>main building, bÃ¢timent principal</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Egyptian 15c support village. Build autonomy and storage first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>phase_1_15c_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>warehouse, entrepÃ´t</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Egyptian 15c support village. Build autonomy and storage first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>phase_1_15c_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Egyptian 15c support village. Build autonomy and storage first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>phase_2_15c_support_online</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bring logistics and feeding capacity online for villages 1 and 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>phase_2_15c_support_online</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>marketplace, marchÃ©</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bring logistics and feeding capacity online for villages 1 and 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>phase_2_15c_support_online</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>warehouse, entrepÃ´t</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bring logistics and feeding capacity online for villages 1 and 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>phase_2_15c_support_online</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bring logistics and feeding capacity online for villages 1 and 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>phase_3_15c_crop_multiplier</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>grain mill, moulin</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Multiply crop output and transport value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>phase_3_15c_crop_multiplier</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>bakery, boulangerie</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Multiply crop output and transport value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>phase_3_15c_crop_multiplier</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Multiply crop output and transport value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>phase_3_15c_crop_multiplier</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>marketplace, marchÃ©</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Multiply crop output and transport value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>phase_4_15c_support_finish</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>warehouse, entrepÃ´t</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Long-term crop battery and logistics backbone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>phase_4_15c_support_finish</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Long-term crop battery and logistics backbone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>phase_4_15c_support_finish</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Long-term crop battery and logistics backbone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>phase_1_roman_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Roman support village focused on clean eco and infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>phase_1_roman_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>main building, bÃ¢timent principal</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Roman support village focused on clean eco and infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>phase_1_roman_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>warehouse, entrepÃ´t</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Roman support village focused on clean eco and infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>phase_1_roman_support_bootstrap</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Roman support village focused on clean eco and infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>phase_2_roman_support_online</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Make it a flexible shipment and support node.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>phase_2_roman_support_online</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>marketplace, marchÃ©</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Make it a flexible shipment and support node.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>phase_2_roman_support_online</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>warehouse, entrepÃ´t</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Make it a flexible shipment and support node.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>phase_2_roman_support_online</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>granary, silo</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Make it a flexible shipment and support node.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>phase_3_roman_flex_finish</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>resource_fields</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>slots 1-18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Keep flexible for future settlers, infra or secondary support role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>phase_3_roman_flex_finish</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>main building, bÃ¢timent principal</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Keep flexible for future settlers, infra or secondary support role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>phase_3_roman_flex_finish</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>building_name</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>marketplace, marchÃ©</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Keep flexible for future settlers, infra or secondary support role.</t>
         </is>
       </c>
     </row>
